--- a/templates/meps_customer_template.xlsx
+++ b/templates/meps_customer_template.xlsx
@@ -60,7 +60,7 @@
     <t>MEPS Quota Update - December 2025</t>
   </si>
   <si>
-    <t>This spreadsheet contains data for the safeguard systems for both the European Union and the United Kingdom.</t>
+    <t>This spreadsheet contains data for the steel import quota systems for both the European Union and the United Kingdom.</t>
   </si>
   <si>
     <t>For ease of use the data has been split into separate tabs for each region/nation.</t>
@@ -75,7 +75,7 @@
     <t>The European Union tab includes data on imports of finished steel products into the European Union.</t>
   </si>
   <si>
-    <t>Imports are assigned to one of 29 different product categories.</t>
+    <t>Imports are assigned to one of 30 different product categories.</t>
   </si>
   <si>
     <t>Quotas are administered quarterly on a first-come first-serve basis.</t>
@@ -90,13 +90,13 @@
     <t>Where a nation does not receive a country specific quota their imports are counted in the "Other countries" category.</t>
   </si>
   <si>
-    <t>If a nation receiving a country specific quota completely uses its allowance throughout the year it may use the "Other countries" allowance in the April - June period.</t>
-  </si>
-  <si>
-    <t>From October 7 2022 an annual quota applies to imports of slab and billet from Russia. All other semi-finished material has been banned.</t>
-  </si>
-  <si>
-    <t>Source: EU Tariff quota consultation</t>
+    <t>If a nation with an EU free trade agreement fully uses its country-specific quota, it may draw on the additional "FTA Quota - CSQ" allowance opened for those nations.</t>
+  </si>
+  <si>
+    <t>From 1 July 2026 the EU steel safeguard was replaced by tariff rate quotas under Regulation (EU) 2026/1384. Imports above quota are subject to a 50% duty.</t>
+  </si>
+  <si>
+    <t>Source: Commission Implementing Regulation (EU) 2026/1457 and the EU TARIC database</t>
   </si>
   <si>
     <t>United Kingdom - Tariff Rate Quotas</t>
@@ -105,16 +105,16 @@
     <t>The United Kingdom tab includes data on imports of finished steel products into the United Kingdom.</t>
   </si>
   <si>
-    <t>Imports are assigned to one of 17 different product categories.</t>
-  </si>
-  <si>
-    <t>Where a nation does not receive a country specific quota their imports are counted in the "All others" category.</t>
-  </si>
-  <si>
-    <t>If a nation receiving a country specific quota completely uses its allowance throughout the year it may use the "All others" allowance in the April - June period.</t>
-  </si>
-  <si>
-    <t>Figures are update daily, with the latest available data correct as at the end of the previous working day.</t>
+    <t>Imports are assigned to one of 20 different product categories.</t>
+  </si>
+  <si>
+    <t>Where a nation does not receive a country specific quota their imports are counted in the "Residual" category.</t>
+  </si>
+  <si>
+    <t>Unused quota volumes roll over to the following quarter but do not carry across to the next quota year. Steel originating in Ukraine is exempt from the measure.</t>
+  </si>
+  <si>
+    <t>Figures are updated daily, with the latest available data correct as at the end of the previous working day.</t>
   </si>
   <si>
     <t>Source: UK Integrated Online Tariff</t>
@@ -123,7 +123,7 @@
     <t>Instructions for sorting the data</t>
   </si>
   <si>
-    <t>Clicking the bars in the slicers at the top of the table will filter the data by Quota Category, Country or Quota Allowance Granted.</t>
+    <t>Clicking the bars in the slicers at the top of the table will filter the data by Quota Category or Country.</t>
   </si>
   <si>
     <t>Slicer filters can be applied separately, combined or cleared.</t>
@@ -147,10 +147,9 @@
     <t>Latest available data: 12-Dec-2025</t>
   </si>
   <si>
-    <t>Following the introduction of individual country caps under the EU import safeguard measures for nations covered by the "other countries" quota, MEPS now provides a detailed breakdown of the relevant quota allocations across affected product categories.
-Nations granted an order number within an "other countries" quota are marked with an *. The figure in the “Quota Limit (Tonnes)” column shows these nations' maximum allocation of the “other countries” quota. This is operated on a first-come, first-serve basis. If the quota limit is reached before their allocation is used, then the 25% above-quota tariff may be applied. Please note that this is not an exhaustive list of the nations which fall within the “other countries” quota.
-The European Commission has adjusted steel safeguard measures for Category "Angles, shapes, and sections of iron or non-alloy steel". The change, implemented on August 1, includes the reintroduction of country-specific quotas for South Korea, Turkey and the United Kingdom.
-For other countries importing under the residual quota, the usage cap will rise from 15% to 40%.</t>
+    <t xml:space="preserve">From 1 July 2026 the EU's steel safeguard was replaced by tariff rate quotas opened under Regulation (EU) 2026/1384 and distributed by Implementing Regulation (EU) 2026/1457.
+Each product category provides country-specific quotas for major supplying nations plus residual allowances. A country-specific quota combines an MFN part and, for free trade agreement partners, an FTA part, accessed under a single order number. FTA partners whose country-specific quota is exhausted may draw on the additional "FTA Quota - CSQ" allowance. Nations without a country-specific quota import under the "Other countries" allowance and, for FTA partners, the "FTA Quota - Other countries" allowance.
+Quotas are managed quarterly on a first-come, first-served basis, and unused balances transfer to the following quarter. Imports above quota are subject to a 50% duty.</t>
   </si>
   <si>
     <t>Quota Category</t>
@@ -384,10 +383,9 @@
     <t>MEPS United Kingdom Quota Update</t>
   </si>
   <si>
-    <t xml:space="preserve">Following the introduction of individual country caps under the UK import safeguard measures for nations covered by the "other countries" quota, MEPS now provides a detailed breakdown of the relevant quota allocations across affected product categories.
-Nations granted an order number within an "other countries" quota are marked with an *. The figure in the “Quota Limit (Tonnes)” column shows these nations' maximum allocation of the “other countries” quota. This is operated on a first-come, first-serve basis. If the quota limit is reached before their allocation is used, then the 25% above-quota tariff may be applied. Please note that this is not an exhaustive list of the nations which fall within the “other countries” quota.
-HMRC temporarily paused the allocation of import quotas for certain countries covered by the individual country cap within the "All others" quota with clearances suspended until August 1, 2025. The numbers in the spreadsheet are those published by the HMRC.
-</t>
+    <t xml:space="preserve">From 1 July 2026 the UK's steel safeguard was replaced by a new steel trade measure implemented under the Taxation (Cross-Border Trade) Act 2018, with overall quota volumes reduced by around 51% compared with the safeguard.
+Quotas are allocated quarterly (July-September, October-December, January-March, April-June) on a first-come, first-served basis. Unused volumes roll over to the next quarter but not to the next quota year. Imports above quota are subject to a 50% duty. Steel originating in Ukraine is exempt from the measure, and goods contracted before 14 March 2026 are exempt during the July-September 2026 transition period (evidence required).
+Category 1 (hot-rolled sheet and strip) also has a separate authorised-use quota for downstream processing, subject to a 40% per-country quarterly cap.</t>
   </si>
   <si>
     <t>Non-alloy and other alloy hot-rolled sheet and strip 1A</t>
@@ -1622,18 +1620,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{ABB843BB-6D4C-413D-9459-234F25C2F640}" name="EU_Quotas4" displayName="EU_Quotas4" ref="A15:G204" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A15:G204" xr:uid="{E868E768-6237-458A-90D6-C15D3AA0A2D9}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Electrical Sheets (other than GOES) - 3a"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Iran, Islamic Republic of"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A15:G204" xr:uid="{E868E768-6237-458A-90D6-C15D3AA0A2D9}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{B473FDE6-67DB-44AB-82D0-62A9576B1E19}" name="Quota Category" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{99A5909C-6233-411A-8FED-2CA191C65C68}" name="Country" dataDxfId="14"/>
